--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_6.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_6.xlsx
@@ -592,7 +592,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>29</v>
@@ -891,7 +891,7 @@
         <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>54</v>
